--- a/data/trans_orig/P17A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2007</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38066</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61516</t>
+          <t>63078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52503</t>
+          <t>53128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80244</t>
+          <t>80429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97572</t>
+          <t>97835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135185</t>
+          <t>135747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>211494</t>
+          <t>209932</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>234944</t>
+          <t>235182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180594</t>
+          <t>180409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>208335</t>
+          <t>207710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>398663</t>
+          <t>398101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436276</t>
+          <t>436013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>72656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106347</t>
+          <t>108973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112980</t>
+          <t>113522</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152041</t>
+          <t>152600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>199986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248099</t>
+          <t>252362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>386728</t>
+          <t>384102</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420951</t>
+          <t>420419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351908</t>
+          <t>351349</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>390969</t>
+          <t>390427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>748925</t>
+          <t>744662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>800573</t>
+          <t>797038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42507</t>
+          <t>42150</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69155</t>
+          <t>69221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85131</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118136</t>
+          <t>117647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134090</t>
+          <t>134957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177926</t>
+          <t>178139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249691</t>
+          <t>249625</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276339</t>
+          <t>276696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>215264</t>
+          <t>215753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248269</t>
+          <t>248582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>474320</t>
+          <t>474107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>518156</t>
+          <t>517289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>42195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66245</t>
+          <t>67739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102526</t>
+          <t>101220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136579</t>
+          <t>138084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>151987</t>
+          <t>150511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196777</t>
+          <t>196106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292426</t>
+          <t>290932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317373</t>
+          <t>316476</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234877</t>
+          <t>233372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268930</t>
+          <t>270236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>533350</t>
+          <t>534021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578140</t>
+          <t>579616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>34332</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57168</t>
+          <t>57447</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62542</t>
+          <t>61492</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90786</t>
+          <t>90997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103525</t>
+          <t>102744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139216</t>
+          <t>139826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146140</t>
+          <t>145861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168848</t>
+          <t>168976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116882</t>
+          <t>116671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145126</t>
+          <t>146176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271760</t>
+          <t>271150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307451</t>
+          <t>308232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35076</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58938</t>
+          <t>58654</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70532</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103418</t>
+          <t>102293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112643</t>
+          <t>112870</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152046</t>
+          <t>152568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211873</t>
+          <t>212157</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235735</t>
+          <t>235638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174726</t>
+          <t>175851</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207612</t>
+          <t>206901</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>396909</t>
+          <t>396387</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>436312</t>
+          <t>436085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,44%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121175</t>
+          <t>123633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164029</t>
+          <t>166821</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193532</t>
+          <t>191860</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>240891</t>
+          <t>238197</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>328354</t>
+          <t>327252</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>392579</t>
+          <t>389946</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>448329</t>
+          <t>445537</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>491183</t>
+          <t>488725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>397328</t>
+          <t>400022</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>444687</t>
+          <t>446359</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>857998</t>
+          <t>860631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>922223</t>
+          <t>923325</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>156775</t>
+          <t>158329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>204504</t>
+          <t>202540</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226057</t>
+          <t>224690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>279730</t>
+          <t>275843</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>397746</t>
+          <t>394828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>469177</t>
+          <t>469207</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>539291</t>
+          <t>541255</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>587020</t>
+          <t>585466</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>503781</t>
+          <t>507668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>557454</t>
+          <t>558821</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1058129</t>
+          <t>1058099</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1129560</t>
+          <t>1132478</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>617762</t>
+          <t>610391</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>705959</t>
+          <t>701611</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>997604</t>
+          <t>989297</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1105986</t>
+          <t>1095103</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1636471</t>
+          <t>1642244</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1788573</t>
+          <t>1780854</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2567915</t>
+          <t>2572263</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2656112</t>
+          <t>2663483</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2271199</t>
+          <t>2282082</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2379581</t>
+          <t>2387888</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4862486</t>
+          <t>4870205</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5014588</t>
+          <t>5008815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,31%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2012</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2012 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49351</t>
+          <t>48491</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78000</t>
+          <t>77202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80055</t>
+          <t>78682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112517</t>
+          <t>111428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134601</t>
+          <t>136640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178510</t>
+          <t>180498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>216738</t>
+          <t>217536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245387</t>
+          <t>246247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>174728</t>
+          <t>175817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207190</t>
+          <t>208563</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>403473</t>
+          <t>401485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>447382</t>
+          <t>445343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84471</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123824</t>
+          <t>126852</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134354</t>
+          <t>135454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177907</t>
+          <t>178809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231418</t>
+          <t>233665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289284</t>
+          <t>292129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374765</t>
+          <t>371737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414118</t>
+          <t>411519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344849</t>
+          <t>343947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>388402</t>
+          <t>387302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>732061</t>
+          <t>729216</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>789927</t>
+          <t>787680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,12%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70258</t>
+          <t>71063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103230</t>
+          <t>104122</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125652</t>
+          <t>124334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163300</t>
+          <t>161628</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203333</t>
+          <t>205438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>256697</t>
+          <t>254617</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220816</t>
+          <t>219924</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253788</t>
+          <t>252983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177720</t>
+          <t>179392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215368</t>
+          <t>216686</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>408369</t>
+          <t>410449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>461733</t>
+          <t>459628</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,11%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56483</t>
+          <t>54738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87740</t>
+          <t>87879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95023</t>
+          <t>96441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131636</t>
+          <t>132919</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160979</t>
+          <t>159927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208912</t>
+          <t>207450</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285257</t>
+          <t>285118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316514</t>
+          <t>318259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>250254</t>
+          <t>248971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>286867</t>
+          <t>285449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>545975</t>
+          <t>547437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593908</t>
+          <t>594960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>40305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66056</t>
+          <t>65758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77084</t>
+          <t>76896</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106031</t>
+          <t>106509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123324</t>
+          <t>122490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163402</t>
+          <t>164385</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145547</t>
+          <t>145845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171760</t>
+          <t>171298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113560</t>
+          <t>113082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142507</t>
+          <t>142695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267792</t>
+          <t>266809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307870</t>
+          <t>308704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65633</t>
+          <t>66652</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94933</t>
+          <t>96044</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94112</t>
+          <t>94419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125032</t>
+          <t>125110</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>167840</t>
+          <t>167363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>211892</t>
+          <t>211701</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179048</t>
+          <t>177937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208348</t>
+          <t>207329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154048</t>
+          <t>153970</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184968</t>
+          <t>184661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341169</t>
+          <t>341360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385221</t>
+          <t>385698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145729</t>
+          <t>146797</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>193119</t>
+          <t>192626</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>200149</t>
+          <t>199296</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251180</t>
+          <t>247814</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>358378</t>
+          <t>358117</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>426366</t>
+          <t>423724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>468772</t>
+          <t>469265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>516162</t>
+          <t>515094</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>442673</t>
+          <t>446039</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>493704</t>
+          <t>494557</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>929378</t>
+          <t>932020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>997366</t>
+          <t>997627</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133490</t>
+          <t>134179</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181618</t>
+          <t>180320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>199283</t>
+          <t>196335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249123</t>
+          <t>249600</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>347227</t>
+          <t>344612</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>416566</t>
+          <t>417047</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>593400</t>
+          <t>594698</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>641528</t>
+          <t>640839</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>572679</t>
+          <t>572202</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>622519</t>
+          <t>625467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1180254</t>
+          <t>1179773</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1249593</t>
+          <t>1252208</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>727602</t>
+          <t>730173</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>831428</t>
+          <t>831885</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1099220</t>
+          <t>1101719</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1215417</t>
+          <t>1213743</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1852918</t>
+          <t>1869143</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2008479</t>
+          <t>2015001</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2581435</t>
+          <t>2580978</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2685261</t>
+          <t>2682690</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2331821</t>
+          <t>2333495</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2448018</t>
+          <t>2445519</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4951622</t>
+          <t>4945100</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5107183</t>
+          <t>5090958</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2016</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55823</t>
+          <t>54653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86454</t>
+          <t>84588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78636</t>
+          <t>76824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111342</t>
+          <t>109271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141865</t>
+          <t>140103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186166</t>
+          <t>186633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>207307</t>
+          <t>209173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237938</t>
+          <t>239108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177361</t>
+          <t>179432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210067</t>
+          <t>211879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>396298</t>
+          <t>395831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>440599</t>
+          <t>442361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92460</t>
+          <t>92625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131284</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161227</t>
+          <t>158613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205513</t>
+          <t>202954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263011</t>
+          <t>260458</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324835</t>
+          <t>321987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371291</t>
+          <t>371392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410115</t>
+          <t>409950</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317571</t>
+          <t>320130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361857</t>
+          <t>364471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700824</t>
+          <t>703672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>762648</t>
+          <t>765201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61733</t>
+          <t>60297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90374</t>
+          <t>89417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87005</t>
+          <t>88552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122464</t>
+          <t>122984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157793</t>
+          <t>156226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203908</t>
+          <t>201825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228191</t>
+          <t>229148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256832</t>
+          <t>258268</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213845</t>
+          <t>213325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>249304</t>
+          <t>247757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>450966</t>
+          <t>453049</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>497081</t>
+          <t>498648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73864</t>
+          <t>73004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106477</t>
+          <t>106935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117782</t>
+          <t>117570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156359</t>
+          <t>156097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199905</t>
+          <t>200765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252789</t>
+          <t>253883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263487</t>
+          <t>263029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296100</t>
+          <t>296960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230924</t>
+          <t>231186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>269501</t>
+          <t>269713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>504458</t>
+          <t>503364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557342</t>
+          <t>556482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40963</t>
+          <t>40431</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>40634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64476</t>
+          <t>64734</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66858</t>
+          <t>65629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98553</t>
+          <t>98670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170258</t>
+          <t>170790</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189791</t>
+          <t>189841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154111</t>
+          <t>153853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179263</t>
+          <t>177953</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331255</t>
+          <t>331138</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>362950</t>
+          <t>364179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92322</t>
+          <t>90351</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123120</t>
+          <t>124173</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113317</t>
+          <t>114224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>146753</t>
+          <t>147919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>213832</t>
+          <t>213554</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>260889</t>
+          <t>261227</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140003</t>
+          <t>138950</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170801</t>
+          <t>172772</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126362</t>
+          <t>125196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159798</t>
+          <t>158891</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275349</t>
+          <t>275011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>322406</t>
+          <t>322684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126287</t>
+          <t>128481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>171287</t>
+          <t>173043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164145</t>
+          <t>163286</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>212599</t>
+          <t>211446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>305356</t>
+          <t>300721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374180</t>
+          <t>372252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>485271</t>
+          <t>483515</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>530271</t>
+          <t>528077</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>478695</t>
+          <t>479848</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527149</t>
+          <t>528008</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>973672</t>
+          <t>975600</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1042496</t>
+          <t>1047131</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199553</t>
+          <t>198725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>247910</t>
+          <t>248026</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>249340</t>
+          <t>252178</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>307984</t>
+          <t>307372</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>469631</t>
+          <t>461517</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>544191</t>
+          <t>540034</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>530673</t>
+          <t>530557</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>579030</t>
+          <t>579858</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>518183</t>
+          <t>518795</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>576827</t>
+          <t>573989</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1060559</t>
+          <t>1064716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1135119</t>
+          <t>1143233</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,24%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>798675</t>
+          <t>799914</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>905200</t>
+          <t>906779</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1104722</t>
+          <t>1110662</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1218369</t>
+          <t>1227594</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1942331</t>
+          <t>1941723</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2101129</t>
+          <t>2090482</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2489150</t>
+          <t>2487571</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2595675</t>
+          <t>2594436</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2326173</t>
+          <t>2316948</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2439820</t>
+          <t>2433880</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4837763</t>
+          <t>4848410</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4996561</t>
+          <t>4997169</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consultado con algún médico (público o privado) por agún problema, molestia o enfermedad suya en las últimas dos semanas en 2023</t>
+          <t>Población que ha tenido una consulta médica (pública o privada) por algún problema, molestia o enfermedad suya en las últimas 2 semanas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52946</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90537</t>
+          <t>91250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62423</t>
+          <t>64302</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87133</t>
+          <t>90125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125573</t>
+          <t>125306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171319</t>
+          <t>170509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220906</t>
+          <t>220193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258497</t>
+          <t>256694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201513</t>
+          <t>198521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>226223</t>
+          <t>224344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>428770</t>
+          <t>429580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>474516</t>
+          <t>474783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>65236</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102637</t>
+          <t>103284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,82 +11060,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>96653</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>82282</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>114229</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>15,98%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>22,18%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>178890</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>152571</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>204765</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>17,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>19,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>96653</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>80996</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>114668</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>22,27%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>178890</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>154695</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>206059</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>17,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>14,98%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414936</t>
+          <t>414289</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452942</t>
+          <t>452337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,82 +11173,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>80,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>418316</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>400740</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>432687</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>77,82%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>84,02%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>853652</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>827777</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>879971</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>82,67%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>80,17%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>418316</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>400301</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>433973</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>77,73%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>853652</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>826483</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>877847</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>82,67%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>80,04%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78648</t>
+          <t>76724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64076</t>
+          <t>63191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90182</t>
+          <t>89203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120596</t>
+          <t>120197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158033</t>
+          <t>158467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237402</t>
+          <t>239326</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>265286</t>
+          <t>265775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258946</t>
+          <t>259925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285052</t>
+          <t>285937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507145</t>
+          <t>506711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>544582</t>
+          <t>544981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>54691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87461</t>
+          <t>88119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110014</t>
+          <t>107930</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>293165</t>
+          <t>280018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176573</t>
+          <t>177203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>393371</t>
+          <t>389559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225096</t>
+          <t>224438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257826</t>
+          <t>257866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182154</t>
+          <t>195301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365305</t>
+          <t>367389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394504</t>
+          <t>398316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>611302</t>
+          <t>610672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26439</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37628</t>
+          <t>37341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57533</t>
+          <t>56650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152303</t>
+          <t>153358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166620</t>
+          <t>166420</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170757</t>
+          <t>172457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185336</t>
+          <t>186214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329012</t>
+          <t>329895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>348917</t>
+          <t>349204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41605</t>
+          <t>41237</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65204</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95968</t>
+          <t>96205</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126851</t>
+          <t>128120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204432</t>
+          <t>204951</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228031</t>
+          <t>228399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187547</t>
+          <t>187928</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208150</t>
+          <t>208196</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>399841</t>
+          <t>398572</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>430724</t>
+          <t>430487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>119129</t>
+          <t>119500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166765</t>
+          <t>167981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96579</t>
+          <t>96681</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>267256</t>
+          <t>266981</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>225450</t>
+          <t>215058</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>410528</t>
+          <t>407238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>457514</t>
+          <t>456298</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>505150</t>
+          <t>504779</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>580885</t>
+          <t>581160</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>751562</t>
+          <t>751460</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1061892</t>
+          <t>1065182</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1246970</t>
+          <t>1257362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>62006</t>
+          <t>55091</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>200866</t>
+          <t>200790</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>178576</t>
+          <t>175717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218892</t>
+          <t>218814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>200457</t>
+          <t>216706</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>405920</t>
+          <t>409777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>727234</t>
+          <t>727310</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>866094</t>
+          <t>873009</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>498680</t>
+          <t>498758</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>538996</t>
+          <t>541855</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1239751</t>
+          <t>1235894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1445214</t>
+          <t>1428965</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>487465</t>
+          <t>483831</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>704610</t>
+          <t>712631</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>765541</t>
+          <t>758693</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1041671</t>
+          <t>1050300</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1356635</t>
+          <t>1355095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1718072</t>
+          <t>1718603</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2753769</t>
+          <t>2745748</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2970914</t>
+          <t>2974548</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2616962</t>
+          <t>2608333</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2893092</t>
+          <t>2899940</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5398940</t>
+          <t>5398409</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5760377</t>
+          <t>5761917</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P17A-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37828</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63078</t>
+          <t>63797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>53174</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80429</t>
+          <t>81096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97835</t>
+          <t>97868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135747</t>
+          <t>135569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209932</t>
+          <t>209213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235182</t>
+          <t>234377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180409</t>
+          <t>179742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207710</t>
+          <t>207664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>398101</t>
+          <t>398279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436013</t>
+          <t>435980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72656</t>
+          <t>72549</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108973</t>
+          <t>107612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>113522</t>
+          <t>113104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152600</t>
+          <t>151794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>199986</t>
+          <t>196190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>252362</t>
+          <t>250557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384102</t>
+          <t>385463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420419</t>
+          <t>420526</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351349</t>
+          <t>352155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>390427</t>
+          <t>390845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>744662</t>
+          <t>746467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>797038</t>
+          <t>800834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42150</t>
+          <t>41234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69221</t>
+          <t>68748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84818</t>
+          <t>86080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117647</t>
+          <t>118260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134957</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178139</t>
+          <t>176367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249625</t>
+          <t>250098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276696</t>
+          <t>277612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>215753</t>
+          <t>215140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>248582</t>
+          <t>247320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>474107</t>
+          <t>475879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>517289</t>
+          <t>518573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42195</t>
+          <t>40299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67739</t>
+          <t>65824</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101220</t>
+          <t>102568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138084</t>
+          <t>138303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150511</t>
+          <t>151078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196106</t>
+          <t>193630</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290932</t>
+          <t>292847</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316476</t>
+          <t>318372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>233372</t>
+          <t>233153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>270236</t>
+          <t>268888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>534021</t>
+          <t>536497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>579616</t>
+          <t>579049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34332</t>
+          <t>34359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57447</t>
+          <t>57640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61492</t>
+          <t>62363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90997</t>
+          <t>90884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>104116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139826</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145861</t>
+          <t>145668</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168976</t>
+          <t>168949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116671</t>
+          <t>116784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146176</t>
+          <t>145305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271150</t>
+          <t>271012</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308232</t>
+          <t>306860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,67%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35173</t>
+          <t>35857</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58654</t>
+          <t>60664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>71243</t>
+          <t>71090</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102293</t>
+          <t>101798</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112870</t>
+          <t>112117</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152568</t>
+          <t>152667</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212157</t>
+          <t>210147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235638</t>
+          <t>234954</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175851</t>
+          <t>176346</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206901</t>
+          <t>207054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>396387</t>
+          <t>396288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>436085</t>
+          <t>436838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123633</t>
+          <t>124490</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166821</t>
+          <t>166268</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>191860</t>
+          <t>191445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>237466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327252</t>
+          <t>328178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>389946</t>
+          <t>392468</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>445537</t>
+          <t>446090</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>488725</t>
+          <t>487868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>400022</t>
+          <t>400753</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>446359</t>
+          <t>446774</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>860631</t>
+          <t>858109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>923325</t>
+          <t>922399</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>158329</t>
+          <t>156729</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>202540</t>
+          <t>205030</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>224690</t>
+          <t>226494</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275843</t>
+          <t>280202</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>394828</t>
+          <t>395603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>469207</t>
+          <t>470214</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>541255</t>
+          <t>538765</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>585466</t>
+          <t>587066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>507668</t>
+          <t>503309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>558821</t>
+          <t>557017</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1058099</t>
+          <t>1057092</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1132478</t>
+          <t>1131703</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>610391</t>
+          <t>615137</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>701611</t>
+          <t>706471</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>989297</t>
+          <t>994968</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1095103</t>
+          <t>1102982</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1642244</t>
+          <t>1635480</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1780854</t>
+          <t>1776710</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2572263</t>
+          <t>2567403</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2663483</t>
+          <t>2658737</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2282082</t>
+          <t>2274203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2387888</t>
+          <t>2382217</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4870205</t>
+          <t>4874349</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5008815</t>
+          <t>5015579</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48491</t>
+          <t>46785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77202</t>
+          <t>76556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78682</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111428</t>
+          <t>113823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136640</t>
+          <t>137071</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180498</t>
+          <t>183753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>217536</t>
+          <t>218182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246247</t>
+          <t>247953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>175817</t>
+          <t>173422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>208563</t>
+          <t>207204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>401485</t>
+          <t>398230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>445343</t>
+          <t>444912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,45%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>85097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126852</t>
+          <t>124800</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135454</t>
+          <t>135134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178809</t>
+          <t>177738</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233665</t>
+          <t>233604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>292129</t>
+          <t>292834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371737</t>
+          <t>373789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411519</t>
+          <t>413492</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343947</t>
+          <t>345018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>387302</t>
+          <t>387622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729216</t>
+          <t>728511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>787680</t>
+          <t>787741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71063</t>
+          <t>71657</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104122</t>
+          <t>104259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124334</t>
+          <t>125603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161628</t>
+          <t>163009</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205438</t>
+          <t>205807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254617</t>
+          <t>254956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>219924</t>
+          <t>219787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>252983</t>
+          <t>252389</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179392</t>
+          <t>178011</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216686</t>
+          <t>215417</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>410449</t>
+          <t>410110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>459628</t>
+          <t>459259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54738</t>
+          <t>56546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87879</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96441</t>
+          <t>96775</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132919</t>
+          <t>132868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159927</t>
+          <t>162940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>207450</t>
+          <t>209062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>285118</t>
+          <t>284808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>318259</t>
+          <t>316451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>248971</t>
+          <t>249022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>285449</t>
+          <t>285115</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>547437</t>
+          <t>545825</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594960</t>
+          <t>591947</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,42%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40305</t>
+          <t>38805</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65758</t>
+          <t>65707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76896</t>
+          <t>76685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106509</t>
+          <t>104537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122490</t>
+          <t>122861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164385</t>
+          <t>163847</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145845</t>
+          <t>145896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171298</t>
+          <t>172798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113082</t>
+          <t>115054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142695</t>
+          <t>142906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>266809</t>
+          <t>267347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308704</t>
+          <t>308333</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66652</t>
+          <t>67124</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96044</t>
+          <t>97212</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94419</t>
+          <t>94173</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125110</t>
+          <t>127151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>167363</t>
+          <t>169460</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>211701</t>
+          <t>215172</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,91%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177937</t>
+          <t>176769</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207329</t>
+          <t>206857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153970</t>
+          <t>151929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184661</t>
+          <t>184907</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341360</t>
+          <t>337889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385698</t>
+          <t>383601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146797</t>
+          <t>144335</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>192626</t>
+          <t>189856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>199296</t>
+          <t>196901</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247814</t>
+          <t>248367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>358117</t>
+          <t>355312</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>423724</t>
+          <t>427053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>469265</t>
+          <t>472035</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>515094</t>
+          <t>517556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>446039</t>
+          <t>445486</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>494557</t>
+          <t>496952</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>932020</t>
+          <t>928691</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>997627</t>
+          <t>1000432</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134179</t>
+          <t>133715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180320</t>
+          <t>181031</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>196335</t>
+          <t>197475</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249600</t>
+          <t>253823</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>344612</t>
+          <t>344010</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>417047</t>
+          <t>415222</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>594698</t>
+          <t>593987</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>640839</t>
+          <t>641303</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>572202</t>
+          <t>567979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>625467</t>
+          <t>624327</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1179773</t>
+          <t>1181598</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1252208</t>
+          <t>1252810</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>730173</t>
+          <t>728996</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>831885</t>
+          <t>833045</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1101719</t>
+          <t>1099160</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1213743</t>
+          <t>1211669</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1869143</t>
+          <t>1859772</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2015001</t>
+          <t>2011120</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2580978</t>
+          <t>2579818</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2682690</t>
+          <t>2683867</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2333495</t>
+          <t>2335569</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2445519</t>
+          <t>2448078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4945100</t>
+          <t>4948981</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5090958</t>
+          <t>5100329</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54653</t>
+          <t>54571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84588</t>
+          <t>85427</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76824</t>
+          <t>77825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109271</t>
+          <t>111636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140103</t>
+          <t>139261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186633</t>
+          <t>183879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209173</t>
+          <t>208334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239108</t>
+          <t>239190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179432</t>
+          <t>177067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>211879</t>
+          <t>210878</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>395831</t>
+          <t>398585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442361</t>
+          <t>443203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92625</t>
+          <t>91341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131183</t>
+          <t>129069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158613</t>
+          <t>159761</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>202954</t>
+          <t>204131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260458</t>
+          <t>261845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321987</t>
+          <t>320513</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>371392</t>
+          <t>373506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409950</t>
+          <t>411234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>320130</t>
+          <t>318953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364471</t>
+          <t>363323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703672</t>
+          <t>705146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>765201</t>
+          <t>763814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,47%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60297</t>
+          <t>60789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89417</t>
+          <t>89711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88552</t>
+          <t>89288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122984</t>
+          <t>122811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156226</t>
+          <t>159171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201825</t>
+          <t>203943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>229148</t>
+          <t>228854</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>258268</t>
+          <t>257776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213325</t>
+          <t>213498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247757</t>
+          <t>247021</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>453049</t>
+          <t>450931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>498648</t>
+          <t>495703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73004</t>
+          <t>73407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106935</t>
+          <t>107662</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117570</t>
+          <t>117294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156097</t>
+          <t>154651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200765</t>
+          <t>198590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>253883</t>
+          <t>248709</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263029</t>
+          <t>262302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296960</t>
+          <t>296557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231186</t>
+          <t>232632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>269713</t>
+          <t>269989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>503364</t>
+          <t>508538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556482</t>
+          <t>558657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>20920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>42498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40634</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64734</t>
+          <t>64372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65629</t>
+          <t>67886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98670</t>
+          <t>100625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170790</t>
+          <t>168723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189841</t>
+          <t>190301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>153853</t>
+          <t>154215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>177953</t>
+          <t>178698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331138</t>
+          <t>329183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364179</t>
+          <t>361922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90351</t>
+          <t>92806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>124173</t>
+          <t>125237</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>114224</t>
+          <t>114079</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147919</t>
+          <t>145237</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>213554</t>
+          <t>216274</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>261227</t>
+          <t>260503</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138950</t>
+          <t>137886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>172772</t>
+          <t>170317</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125196</t>
+          <t>127878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158891</t>
+          <t>159036</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275011</t>
+          <t>275735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>322684</t>
+          <t>319964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>128481</t>
+          <t>127398</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173043</t>
+          <t>174156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163286</t>
+          <t>163228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>211150</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>300721</t>
+          <t>302900</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>372252</t>
+          <t>370860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>483515</t>
+          <t>482402</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>528077</t>
+          <t>529160</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>479848</t>
+          <t>480144</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>528008</t>
+          <t>528066</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>975600</t>
+          <t>976992</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1047131</t>
+          <t>1044952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198725</t>
+          <t>200198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>248026</t>
+          <t>253690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>252178</t>
+          <t>252070</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>307372</t>
+          <t>310059</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>461517</t>
+          <t>465612</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>540034</t>
+          <t>538220</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>530557</t>
+          <t>524893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>579858</t>
+          <t>578385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>518795</t>
+          <t>516108</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>573989</t>
+          <t>574097</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1064716</t>
+          <t>1066530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1143233</t>
+          <t>1139138</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>799914</t>
+          <t>810478</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>906779</t>
+          <t>907318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1110662</t>
+          <t>1112386</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1227594</t>
+          <t>1217719</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1941723</t>
+          <t>1944005</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2090482</t>
+          <t>2099412</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2487571</t>
+          <t>2487032</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2594436</t>
+          <t>2583872</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2316948</t>
+          <t>2326823</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2433880</t>
+          <t>2432156</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4848410</t>
+          <t>4839480</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4997169</t>
+          <t>4994887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70196</t>
+          <t>65193</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54749</t>
+          <t>52128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91250</t>
+          <t>81539</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>81380</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64302</t>
+          <t>68380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90125</t>
+          <t>95567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>145453</t>
+          <t>146572</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125306</t>
+          <t>129175</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>170509</t>
+          <t>167109</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>241247</t>
+          <t>253652</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220193</t>
+          <t>237306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>256694</t>
+          <t>266717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>213389</t>
+          <t>233695</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198521</t>
+          <t>219508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>224344</t>
+          <t>246695</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>454636</t>
+          <t>487348</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>429580</t>
+          <t>466811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>474783</t>
+          <t>504745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,62%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>288646</t>
+          <t>315075</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>288646</t>
+          <t>315075</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>288646</t>
+          <t>315075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>600089</t>
+          <t>633920</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>600089</t>
+          <t>633920</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>600089</t>
+          <t>633920</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82237</t>
+          <t>84887</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65236</t>
+          <t>66106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103284</t>
+          <t>106784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96653</t>
+          <t>101325</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82282</t>
+          <t>86078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114229</t>
+          <t>118193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,22 +11110,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>178890</t>
+          <t>186213</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152571</t>
+          <t>159063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>204765</t>
+          <t>210241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>435336</t>
+          <t>444854</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414289</t>
+          <t>422957</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>452337</t>
+          <t>463635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>418316</t>
+          <t>445169</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400740</t>
+          <t>428301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432687</t>
+          <t>460416</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,27 +11223,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>853652</t>
+          <t>890023</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>827777</t>
+          <t>865995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>879971</t>
+          <t>917173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517573</t>
+          <t>529741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517573</t>
+          <t>529741</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517573</t>
+          <t>529741</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032542</t>
+          <t>1076236</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032542</t>
+          <t>1076236</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032542</t>
+          <t>1076236</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>64050</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50275</t>
+          <t>52218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76724</t>
+          <t>78762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63191</t>
+          <t>66161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89203</t>
+          <t>91565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>139086</t>
+          <t>142311</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120197</t>
+          <t>123294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158467</t>
+          <t>160771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>252744</t>
+          <t>251943</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239326</t>
+          <t>237231</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>265775</t>
+          <t>263775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>273348</t>
+          <t>278120</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259925</t>
+          <t>264816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>285937</t>
+          <t>290220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>526092</t>
+          <t>530064</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>506711</t>
+          <t>511604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>544981</t>
+          <t>549081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70264</t>
+          <t>84027</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54691</t>
+          <t>66839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88119</t>
+          <t>106182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>169846</t>
+          <t>113332</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107930</t>
+          <t>96213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>280018</t>
+          <t>132216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>240110</t>
+          <t>197359</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177203</t>
+          <t>172166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389559</t>
+          <t>222946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>242293</t>
+          <t>289118</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>224438</t>
+          <t>266963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257866</t>
+          <t>306306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>305473</t>
+          <t>308207</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195301</t>
+          <t>289323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367389</t>
+          <t>325326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>547765</t>
+          <t>597326</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398316</t>
+          <t>571739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>610672</t>
+          <t>622519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475319</t>
+          <t>421539</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475319</t>
+          <t>421539</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475319</t>
+          <t>421539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787875</t>
+          <t>794685</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787875</t>
+          <t>794685</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787875</t>
+          <t>794685</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25384</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,22 +12104,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37341</t>
+          <t>39773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56650</t>
+          <t>61646</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160499</t>
+          <t>186175</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153358</t>
+          <t>177128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166420</t>
+          <t>192193</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>179527</t>
+          <t>196789</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172457</t>
+          <t>188576</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186214</t>
+          <t>202821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>340025</t>
+          <t>382964</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>329895</t>
+          <t>370355</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349204</t>
+          <t>392228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207803</t>
+          <t>226336</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207803</t>
+          <t>226336</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207803</t>
+          <t>226336</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386545</t>
+          <t>432001</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386545</t>
+          <t>432001</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386545</t>
+          <t>432001</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52886</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41237</t>
+          <t>41484</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>64685</t>
+          <t>63749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58387</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48860</t>
+          <t>49354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69128</t>
+          <t>70299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>110822</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96205</t>
+          <t>96196</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>128120</t>
+          <t>126628</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>216750</t>
+          <t>219560</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204951</t>
+          <t>206958</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228399</t>
+          <t>229223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>198669</t>
+          <t>204075</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187928</t>
+          <t>193451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208196</t>
+          <t>214396</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>415419</t>
+          <t>423635</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398572</t>
+          <t>407829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>430487</t>
+          <t>438261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>142546</t>
+          <t>162899</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>119500</t>
+          <t>140234</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167981</t>
+          <t>190186</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>195802</t>
+          <t>241894</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96681</t>
+          <t>218652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>266981</t>
+          <t>266565</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>338348</t>
+          <t>404793</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>215058</t>
+          <t>368813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>407238</t>
+          <t>439859</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>481733</t>
+          <t>556788</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>456298</t>
+          <t>529501</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>504779</t>
+          <t>579453</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>652339</t>
+          <t>529092</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>581160</t>
+          <t>504421</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>751460</t>
+          <t>552334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1134072</t>
+          <t>1085880</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1065182</t>
+          <t>1050814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1257362</t>
+          <t>1121860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848141</t>
+          <t>770986</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848141</t>
+          <t>770986</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848141</t>
+          <t>770986</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472420</t>
+          <t>1490673</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472420</t>
+          <t>1490673</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472420</t>
+          <t>1490673</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>141677</t>
+          <t>158931</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55091</t>
+          <t>138551</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>200790</t>
+          <t>183706</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>196561</t>
+          <t>221206</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175717</t>
+          <t>198220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218814</t>
+          <t>242726</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>338238</t>
+          <t>380138</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>216706</t>
+          <t>351576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>409777</t>
+          <t>414335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>786423</t>
+          <t>638473</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>727310</t>
+          <t>613698</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>873009</t>
+          <t>658853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>521011</t>
+          <t>608858</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>498758</t>
+          <t>587338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>541855</t>
+          <t>631844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1307433</t>
+          <t>1247330</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1235894</t>
+          <t>1213133</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1428965</t>
+          <t>1275892</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928100</t>
+          <t>797404</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830064</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830064</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717572</t>
+          <t>830064</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645671</t>
+          <t>1627468</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645671</t>
+          <t>1627468</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645671</t>
+          <t>1627468</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>483831</t>
+          <t>642263</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>712631</t>
+          <t>746952</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>758693</t>
+          <t>881086</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1050300</t>
+          <t>972095</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1355095</t>
+          <t>1547884</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1718603</t>
+          <t>1683892</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2817024</t>
+          <t>2840564</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2745748</t>
+          <t>2784236</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2974548</t>
+          <t>2888925</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2762071</t>
+          <t>2804006</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2608333</t>
+          <t>2758531</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2899940</t>
+          <t>2849540</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5579095</t>
+          <t>5644570</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5398409</t>
+          <t>5577922</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5761917</t>
+          <t>5713930</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458379</t>
+          <t>3531188</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658633</t>
+          <t>3730626</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7117012</t>
+          <t>7261814</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
